--- a/Backend/public/docs/proveedores-empresas-format-hn.xlsx
+++ b/Backend/public/docs/proveedores-empresas-format-hn.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
   <si>
     <t>nombre_empresa</t>
   </si>
   <si>
-    <t>rtn</t>
+    <t>RTN</t>
   </si>
   <si>
     <t>giro</t>
@@ -29,6 +29,12 @@
     <t>tipo_contribuyente</t>
   </si>
   <si>
+    <t>N. de Identificación</t>
+  </si>
+  <si>
+    <t>nit</t>
+  </si>
+  <si>
     <t>direccion</t>
   </si>
   <si>
@@ -56,6 +62,9 @@
     <t>Grande</t>
   </si>
   <si>
+    <t>0801-1990-00123</t>
+  </si>
+  <si>
     <t>Col. El Trapiche</t>
   </si>
   <si>
@@ -63,6 +72,9 @@
   </si>
   <si>
     <t>Francisco Morazán</t>
+  </si>
+  <si>
+    <t>22622002</t>
   </si>
   <si>
     <t>compras@ejemplo.com</t>
@@ -421,21 +433,23 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,34 +477,46 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>22622002</v>
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/public/docs/proveedores-empresas-format-hn.xlsx
+++ b/Backend/public/docs/proveedores-empresas-format-hn.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
   <si>
     <t>nombre_empresa</t>
   </si>
@@ -48,6 +48,21 @@
   </si>
   <si>
     <t>correo</t>
+  </si>
+  <si>
+    <t>Banco</t>
+  </si>
+  <si>
+    <t>Tipo_cuenta</t>
+  </si>
+  <si>
+    <t>Numero_cuenta</t>
+  </si>
+  <si>
+    <t>Titular_cuenta</t>
+  </si>
+  <si>
+    <t>Forma_pago</t>
   </si>
   <si>
     <t>Proveedor HN SA</t>
@@ -433,23 +448,23 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="18.71" customWidth="true" style="0"/>
+    <col min="2" max="2" width="17.567" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.569" customWidth="true" style="0"/>
+    <col min="4" max="4" width="22.28" customWidth="true" style="0"/>
+    <col min="5" max="5" width="24.708" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.567" customWidth="true" style="0"/>
+    <col min="7" max="7" width="19.995" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.995" customWidth="true" style="0"/>
+    <col min="9" max="9" width="21.138" customWidth="true" style="0"/>
+    <col min="10" max="10" width="10.569" customWidth="true" style="0"/>
+    <col min="11" max="11" width="23.423" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,40 +498,55 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
